--- a/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
@@ -308,7 +308,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" refreshedBy="Jan Havlíček" refreshedDate="45640.183021412035" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{5A3793E0-F24E-4218-978B-ED3C8CBB3606}" mc:Ignorable="xr">
+<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="0" refreshedBy="Jan Havlíček" refreshedDate="45640.183021412035" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{5A3793E0-F24E-4218-978B-ED3C8CBB3606}" mc:Ignorable="xr">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="D3:E4" sheet="Area Source"/>
   </x:cacheSource>
@@ -329,7 +329,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" refreshedBy="Jan Havlíček" refreshedDate="45640.18319664352" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{99F43060-B546-41D9-8AD6-43E3D15EE121}" mc:Ignorable="xr">
+<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="0" refreshedBy="Jan Havlíček" refreshedDate="45640.18319664352" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{99F43060-B546-41D9-8AD6-43E3D15EE121}" mc:Ignorable="xr">
   <x:cacheSource type="worksheet">
     <x:worksheetSource name="Table1"/>
   </x:cacheSource>
@@ -350,7 +350,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" refreshedBy="Jan Havlíček" refreshedDate="45640.183633217595" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{1DDB9D54-7888-42ED-9CF2-85B827247CCD}" mc:Ignorable="xr">
+<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="0" refreshedBy="Jan Havlíček" refreshedDate="45640.183633217595" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{1DDB9D54-7888-42ED-9CF2-85B827247CCD}" mc:Ignorable="xr">
   <x:cacheSource type="worksheet">
     <x:worksheetSource name="AreaName"/>
   </x:cacheSource>
@@ -371,7 +371,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" refreshedBy="Jan Havlíček" refreshedDate="45640.19502673611" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{D6103DA1-26CC-456C-A3F0-D133DC8655B9}" mc:Ignorable="xr">
+<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="0" refreshedBy="Jan Havlíček" refreshedDate="45640.19502673611" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{D6103DA1-26CC-456C-A3F0-D133DC8655B9}" mc:Ignorable="xr">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:B3" sheet="Sheet1" r:id="rId2"/>
   </x:cacheSource>
@@ -392,7 +392,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" refreshedBy="Jan Havlíček" refreshedDate="45640.820318865743" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{08AFD5F3-EF3C-4277-9EC0-BC5F6E36BD65}" mc:Ignorable="xr">
+<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="0" refreshedBy="Jan Havlíček" refreshedDate="45640.820318865743" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{08AFD5F3-EF3C-4277-9EC0-BC5F6E36BD65}" mc:Ignorable="xr">
   <x:cacheSource type="external" connectionId="1"/>
   <x:cacheFields count="2">
     <x:cacheField name="Name">
@@ -417,7 +417,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" saveData="0" refreshOnLoad="1" refreshedBy="Jan Havlíček" refreshedDate="45640.931218171296" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{9BD42A5F-5A0C-417E-AEDF-DBA25499EC16}" mc:Ignorable="xr">
+<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" saveData="0" refreshOnLoad="0" refreshedBy="Jan Havlíček" refreshedDate="45640.931218171296" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{9BD42A5F-5A0C-417E-AEDF-DBA25499EC16}" mc:Ignorable="xr">
   <x:cacheSource type="scenario"/>
   <x:cacheFields count="3">
     <x:cacheField name="$B$2:$B$3">
@@ -447,7 +447,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" refreshedBy="Jan Havlíček" refreshedDate="45641.123992361114" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{C4D000D4-C547-41E9-B0B9-2D56DCDF4F13}" mc:Ignorable="xr">
+<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="0" refreshedBy="Jan Havlíček" refreshedDate="45641.123992361114" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{C4D000D4-C547-41E9-B0B9-2D56DCDF4F13}" mc:Ignorable="xr">
   <x:cacheSource type="consolidation">
     <x:consolidation autoPage="0">
       <x:pages>

--- a/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
@@ -1463,6 +1463,7 @@
       </x:c>
       <x:c r="B5" s="0">
         <x:f>(B2+B3)*1.21</x:f>
+        <x:v>30.25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
@@ -103,6 +103,18 @@
     <x:t>(All)</x:t>
   </x:si>
   <x:si>
+    <x:t>Row Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$B$5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Expensive</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Original</x:t>
+  </x:si>
+  <x:si>
     <x:t>Tax</x:t>
   </x:si>
   <x:si>
@@ -113,6 +125,15 @@
   </x:si>
   <x:si>
     <x:t>Page2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sum of Value</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Column Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Total</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -265,8 +286,35 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1109,10 +1157,100 @@
   <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A4" s="4"/>
+      <x:c r="B4" s="5"/>
+      <x:c r="C4" s="6"/>
+    </x:row>
+    <x:row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A5" s="4"/>
+      <x:c r="B5" s="5"/>
+      <x:c r="C5" s="6"/>
+    </x:row>
+    <x:row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A6" s="4"/>
+      <x:c r="B6" s="5"/>
+      <x:c r="C6" s="6"/>
+    </x:row>
+    <x:row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A7" s="4"/>
+      <x:c r="B7" s="5"/>
+      <x:c r="C7" s="6"/>
+    </x:row>
+    <x:row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A8" s="4"/>
+      <x:c r="B8" s="5"/>
+      <x:c r="C8" s="6"/>
+    </x:row>
+    <x:row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A9" s="4"/>
+      <x:c r="B9" s="5"/>
+      <x:c r="C9" s="6"/>
+    </x:row>
+    <x:row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A10" s="4"/>
+      <x:c r="B10" s="5"/>
+      <x:c r="C10" s="6"/>
+    </x:row>
+    <x:row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="5"/>
+      <x:c r="C11" s="6"/>
+    </x:row>
+    <x:row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="5"/>
+      <x:c r="C12" s="6"/>
+    </x:row>
+    <x:row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="5"/>
+      <x:c r="C13" s="6"/>
+    </x:row>
+    <x:row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="5"/>
+      <x:c r="C14" s="6"/>
+    </x:row>
+    <x:row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A15" s="4"/>
+      <x:c r="B15" s="5"/>
+      <x:c r="C15" s="6"/>
+    </x:row>
+    <x:row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="5"/>
+      <x:c r="C16" s="6"/>
+    </x:row>
+    <x:row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="5"/>
+      <x:c r="C17" s="6"/>
+    </x:row>
+    <x:row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="5"/>
+      <x:c r="C18" s="6"/>
+    </x:row>
+    <x:row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="5"/>
+      <x:c r="C19" s="6"/>
+    </x:row>
+    <x:row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A20" s="7"/>
+      <x:c r="B20" s="8"/>
+      <x:c r="C20" s="9"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1143,6 +1281,30 @@
         <x:v>11</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <x:c r="A4" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>151.25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <x:c r="A5" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>30.25</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1171,7 +1333,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1190,7 +1352,7 @@
     </x:row>
     <x:row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <x:c r="A3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="0">
         <x:v>17</x:v>
@@ -1221,7 +1383,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
         <x:v>11</x:v>
@@ -1229,10 +1391,71 @@
     </x:row>
     <x:row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <x:c r="A2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A6" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>1.21</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>26.21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A7" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D7" s="0">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <x:c r="A8" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>1.21</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D8" s="0">
+        <x:v>43.21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1252,10 +1475,100 @@
   <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A4" s="4"/>
+      <x:c r="B4" s="5"/>
+      <x:c r="C4" s="6"/>
+    </x:row>
+    <x:row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A5" s="4"/>
+      <x:c r="B5" s="5"/>
+      <x:c r="C5" s="6"/>
+    </x:row>
+    <x:row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A6" s="4"/>
+      <x:c r="B6" s="5"/>
+      <x:c r="C6" s="6"/>
+    </x:row>
+    <x:row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A7" s="4"/>
+      <x:c r="B7" s="5"/>
+      <x:c r="C7" s="6"/>
+    </x:row>
+    <x:row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A8" s="4"/>
+      <x:c r="B8" s="5"/>
+      <x:c r="C8" s="6"/>
+    </x:row>
+    <x:row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A9" s="4"/>
+      <x:c r="B9" s="5"/>
+      <x:c r="C9" s="6"/>
+    </x:row>
+    <x:row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A10" s="4"/>
+      <x:c r="B10" s="5"/>
+      <x:c r="C10" s="6"/>
+    </x:row>
+    <x:row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="5"/>
+      <x:c r="C11" s="6"/>
+    </x:row>
+    <x:row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="5"/>
+      <x:c r="C12" s="6"/>
+    </x:row>
+    <x:row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="5"/>
+      <x:c r="C13" s="6"/>
+    </x:row>
+    <x:row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="5"/>
+      <x:c r="C14" s="6"/>
+    </x:row>
+    <x:row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A15" s="4"/>
+      <x:c r="B15" s="5"/>
+      <x:c r="C15" s="6"/>
+    </x:row>
+    <x:row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="5"/>
+      <x:c r="C16" s="6"/>
+    </x:row>
+    <x:row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="5"/>
+      <x:c r="C17" s="6"/>
+    </x:row>
+    <x:row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="5"/>
+      <x:c r="C18" s="6"/>
+    </x:row>
+    <x:row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="5"/>
+      <x:c r="C19" s="6"/>
+    </x:row>
+    <x:row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A20" s="7"/>
+      <x:c r="B20" s="8"/>
+      <x:c r="C20" s="9"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1307,10 +1620,100 @@
   <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A4" s="4"/>
+      <x:c r="B4" s="5"/>
+      <x:c r="C4" s="6"/>
+    </x:row>
+    <x:row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A5" s="4"/>
+      <x:c r="B5" s="5"/>
+      <x:c r="C5" s="6"/>
+    </x:row>
+    <x:row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A6" s="4"/>
+      <x:c r="B6" s="5"/>
+      <x:c r="C6" s="6"/>
+    </x:row>
+    <x:row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A7" s="4"/>
+      <x:c r="B7" s="5"/>
+      <x:c r="C7" s="6"/>
+    </x:row>
+    <x:row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A8" s="4"/>
+      <x:c r="B8" s="5"/>
+      <x:c r="C8" s="6"/>
+    </x:row>
+    <x:row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A9" s="4"/>
+      <x:c r="B9" s="5"/>
+      <x:c r="C9" s="6"/>
+    </x:row>
+    <x:row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A10" s="4"/>
+      <x:c r="B10" s="5"/>
+      <x:c r="C10" s="6"/>
+    </x:row>
+    <x:row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="5"/>
+      <x:c r="C11" s="6"/>
+    </x:row>
+    <x:row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="5"/>
+      <x:c r="C12" s="6"/>
+    </x:row>
+    <x:row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="5"/>
+      <x:c r="C13" s="6"/>
+    </x:row>
+    <x:row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="5"/>
+      <x:c r="C14" s="6"/>
+    </x:row>
+    <x:row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A15" s="4"/>
+      <x:c r="B15" s="5"/>
+      <x:c r="C15" s="6"/>
+    </x:row>
+    <x:row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="5"/>
+      <x:c r="C16" s="6"/>
+    </x:row>
+    <x:row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="5"/>
+      <x:c r="C17" s="6"/>
+    </x:row>
+    <x:row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="5"/>
+      <x:c r="C18" s="6"/>
+    </x:row>
+    <x:row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="5"/>
+      <x:c r="C19" s="6"/>
+    </x:row>
+    <x:row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A20" s="7"/>
+      <x:c r="B20" s="8"/>
+      <x:c r="C20" s="9"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1364,10 +1767,100 @@
   <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A4" s="4"/>
+      <x:c r="B4" s="5"/>
+      <x:c r="C4" s="6"/>
+    </x:row>
+    <x:row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A5" s="4"/>
+      <x:c r="B5" s="5"/>
+      <x:c r="C5" s="6"/>
+    </x:row>
+    <x:row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A6" s="4"/>
+      <x:c r="B6" s="5"/>
+      <x:c r="C6" s="6"/>
+    </x:row>
+    <x:row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A7" s="4"/>
+      <x:c r="B7" s="5"/>
+      <x:c r="C7" s="6"/>
+    </x:row>
+    <x:row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A8" s="4"/>
+      <x:c r="B8" s="5"/>
+      <x:c r="C8" s="6"/>
+    </x:row>
+    <x:row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A9" s="4"/>
+      <x:c r="B9" s="5"/>
+      <x:c r="C9" s="6"/>
+    </x:row>
+    <x:row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A10" s="4"/>
+      <x:c r="B10" s="5"/>
+      <x:c r="C10" s="6"/>
+    </x:row>
+    <x:row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="5"/>
+      <x:c r="C11" s="6"/>
+    </x:row>
+    <x:row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="5"/>
+      <x:c r="C12" s="6"/>
+    </x:row>
+    <x:row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="5"/>
+      <x:c r="C13" s="6"/>
+    </x:row>
+    <x:row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="5"/>
+      <x:c r="C14" s="6"/>
+    </x:row>
+    <x:row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A15" s="4"/>
+      <x:c r="B15" s="5"/>
+      <x:c r="C15" s="6"/>
+    </x:row>
+    <x:row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="5"/>
+      <x:c r="C16" s="6"/>
+    </x:row>
+    <x:row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="5"/>
+      <x:c r="C17" s="6"/>
+    </x:row>
+    <x:row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="5"/>
+      <x:c r="C18" s="6"/>
+    </x:row>
+    <x:row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="5"/>
+      <x:c r="C19" s="6"/>
+    </x:row>
+    <x:row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A20" s="7"/>
+      <x:c r="B20" s="8"/>
+      <x:c r="C20" s="9"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1419,10 +1912,100 @@
   <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
-    <x:row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="2"/>
+      <x:c r="C3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A4" s="4"/>
+      <x:c r="B4" s="5"/>
+      <x:c r="C4" s="6"/>
+    </x:row>
+    <x:row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A5" s="4"/>
+      <x:c r="B5" s="5"/>
+      <x:c r="C5" s="6"/>
+    </x:row>
+    <x:row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A6" s="4"/>
+      <x:c r="B6" s="5"/>
+      <x:c r="C6" s="6"/>
+    </x:row>
+    <x:row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A7" s="4"/>
+      <x:c r="B7" s="5"/>
+      <x:c r="C7" s="6"/>
+    </x:row>
+    <x:row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A8" s="4"/>
+      <x:c r="B8" s="5"/>
+      <x:c r="C8" s="6"/>
+    </x:row>
+    <x:row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A9" s="4"/>
+      <x:c r="B9" s="5"/>
+      <x:c r="C9" s="6"/>
+    </x:row>
+    <x:row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A10" s="4"/>
+      <x:c r="B10" s="5"/>
+      <x:c r="C10" s="6"/>
+    </x:row>
+    <x:row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="5"/>
+      <x:c r="C11" s="6"/>
+    </x:row>
+    <x:row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="5"/>
+      <x:c r="C12" s="6"/>
+    </x:row>
+    <x:row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="5"/>
+      <x:c r="C13" s="6"/>
+    </x:row>
+    <x:row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="5"/>
+      <x:c r="C14" s="6"/>
+    </x:row>
+    <x:row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A15" s="4"/>
+      <x:c r="B15" s="5"/>
+      <x:c r="C15" s="6"/>
+    </x:row>
+    <x:row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A16" s="4"/>
+      <x:c r="B16" s="5"/>
+      <x:c r="C16" s="6"/>
+    </x:row>
+    <x:row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="5"/>
+      <x:c r="C17" s="6"/>
+    </x:row>
+    <x:row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="5"/>
+      <x:c r="C18" s="6"/>
+    </x:row>
+    <x:row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="5"/>
+      <x:c r="C19" s="6"/>
+    </x:row>
+    <x:row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <x:c r="A20" s="7"/>
+      <x:c r="B20" s="8"/>
+      <x:c r="C20" s="9"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
@@ -645,7 +645,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
@@ -661,7 +661,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
@@ -677,7 +677,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
@@ -693,7 +693,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
@@ -709,7 +709,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
@@ -756,7 +756,7 @@
   <dataFields count="1">
     <dataField name="$B$5" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
@@ -834,7 +834,7 @@
   <dataFields count="1">
     <dataField name="Sum of Value" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
